--- a/outputs/analysis_results.xlsx
+++ b/outputs/analysis_results.xlsx
@@ -22,6 +22,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="q12_seller_watchlist" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="q13_opportunity_sizing" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="q14_repeat_purchase" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bt01_recommended_rule" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bt02_threshold_options" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bt03_monthly_alert_volume" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bt04_lead_time" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2887,6 +2891,664 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>risk_tier</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_of_orders</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>late_orders</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>late_rate_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pct_of_all_late_caught</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>avg_review_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8477</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1606</v>
+      </c>
+      <c r="E2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14376</v>
+      </c>
+      <c r="C3" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1297</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>29759</v>
+      </c>
+      <c r="C4" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1173</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>option_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>high_pct_of_orders</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high_late_rate_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>high_catches_pct_of_late</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>high_or_medium_catches_pct_of_late</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>low_late_rate_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>high_alerts_per_day</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>History only (no live signal)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>History + live, HIGH &lt; 0, MEDIUM &lt; 5  [recommended]</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>History + live, HIGH &lt; 2, MEDIUM &lt; 5</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>51</v>
+      </c>
+      <c r="F4" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>History + live, HIGH &lt; 3, MEDIUM &lt; 7</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>year_month</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>late_rate_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high_alerts</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>high_alerts_per_day</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>high_late_rate_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>low_late_rate_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>high_catches_pct_of_late</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2018-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7069</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>767</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6555</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7003</v>
+      </c>
+      <c r="C4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1670</v>
+      </c>
+      <c r="E4" t="n">
+        <v>56</v>
+      </c>
+      <c r="F4" t="n">
+        <v>26</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6791</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1511</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>64.09999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6719</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>713</v>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6050</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>276</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6119</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>704</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>59.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6306</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2280</v>
+      </c>
+      <c r="E9" t="n">
+        <v>76</v>
+      </c>
+      <c r="F9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>90.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>median_days_warning</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>p25_days_warning</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_with_3plus_days_warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>73.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
